--- a/tables/Table S6.xlsx
+++ b/tables/Table S6.xlsx
@@ -1187,32 +1187,32 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>0.19 (0.06)</t>
+          <t>0.21 (0.07)</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>-35.3 (8.9)</t>
+          <t>-38.4 (10.4)</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>-127.1 (38.1)</t>
+          <t>-138.5 (42.5)</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>-350.6 (83.5)</t>
+          <t>-374.5 (86.0)</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>0.9 (0.3)</t>
+          <t>1.0 (0.4)</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>0.0434 (0.0161)</t>
+          <t>0.0497 (0.0178)</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1222,17 +1222,17 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>-15.2 (6.7)</t>
+          <t>-15.4 (3.4)</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>13.9 (6.1)</t>
+          <t>14.9 (6.6)</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>167.3 (22.8)</t>
+          <t>175.6 (22.5)</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>0.0257 (0.0102)</t>
+          <t>0.0271 (0.0062)</t>
         </is>
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>0.0346 (0.0117)</t>
+          <t>0.0384 (0.0108)</t>
         </is>
       </c>
     </row>
@@ -1259,67 +1259,67 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>0.24 (0.07)</t>
+          <t>0.33 (–)</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>-34.4 (16.0)</t>
+          <t>-47.0 (–)</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>-155.0 (45.2)</t>
+          <t>-214.4 (–)</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>-416.4 (94.4)</t>
+          <t>-515.8 (–)</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>1.2 (0.4)</t>
+          <t>1.6 (–)</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>0.0370 (0.0298)</t>
+          <t>0.0770 (–)</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>-0.08 (0.01)</t>
+          <t>-0.09 (–)</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>-18.8 (5.3)</t>
+          <t>-16.8 (–)</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>16.2 (3.9)</t>
+          <t>21.2 (–)</t>
         </is>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>206.4 (23.3)</t>
+          <t>223.2 (–)</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>-0.3 (0.0)</t>
+          <t>-0.3 (–)</t>
         </is>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>0.0276 (0.0082)</t>
+          <t>0.0340 (–)</t>
         </is>
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>0.0323 (0.0174)</t>
+          <t>0.0555 (–)</t>
         </is>
       </c>
     </row>
@@ -1331,67 +1331,67 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>0.24 (0.05)</t>
+          <t>0.28 (–)</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>-30.1 (19.1)</t>
+          <t>-59.4 (–)</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>-150.3 (34.8)</t>
+          <t>-197.8 (–)</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>-418.4 (72.9)</t>
+          <t>-468.0 (–)</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>1.2 (0.3)</t>
+          <t>1.3 (–)</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>0.0242 (0.0203)</t>
+          <t>0.0551 (–)</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>-0.08 (0.01)</t>
+          <t>-0.08 (–)</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>-14.5 (9.9)</t>
+          <t>-16.7 (–)</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>18.4 (5.3)</t>
+          <t>17.5 (–)</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>195.7 (26.8)</t>
+          <t>206.1 (–)</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>-0.3 (0.0)</t>
+          <t>-0.3 (–)</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>0.0224 (0.0171)</t>
+          <t>0.0219 (–)</t>
         </is>
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>0.0233 (0.0135)</t>
+          <t>0.0385 (–)</t>
         </is>
       </c>
     </row>
@@ -1403,67 +1403,67 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>0.16 (0.06)</t>
+          <t>0.19 (0.07)</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>-27.9 (24.3)</t>
+          <t>-38.8 (27.9)</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>-104.3 (45.8)</t>
+          <t>-128.5 (56.8)</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>-305.8 (92.6)</t>
+          <t>-347.9 (97.5)</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>0.7 (0.3)</t>
+          <t>0.9 (0.3)</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>0.0278 (0.0365)</t>
+          <t>0.0479 (0.0407)</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>-0.06 (0.01)</t>
+          <t>-0.06 (0.00)</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>-11.7 (5.6)</t>
+          <t>-9.5 (4.6)</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>14.8 (4.2)</t>
+          <t>17.3 (2.9)</t>
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>151.7 (34.3)</t>
+          <t>152.8 (8.8)</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>-0.2 (0.1)</t>
+          <t>-0.2 (0.0)</t>
         </is>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>0.0180 (0.0068)</t>
+          <t>0.0172 (0.0071)</t>
         </is>
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>0.0229 (0.0201)</t>
+          <t>0.0326 (0.0233)</t>
         </is>
       </c>
     </row>

--- a/tables/Table S6.xlsx
+++ b/tables/Table S6.xlsx
@@ -579,7 +579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:T20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="9.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -591,13 +591,17 @@
     <col width="10.33203125" bestFit="1" customWidth="1" min="7" max="7"/>
     <col width="6.5" bestFit="1" customWidth="1" min="8" max="8"/>
     <col width="10.1640625" bestFit="1" customWidth="1" min="9" max="9"/>
-    <col width="8.6640625" bestFit="1" customWidth="1" min="10" max="10"/>
-    <col width="10.6640625" customWidth="1" min="11" max="11"/>
-    <col width="11.33203125" bestFit="1" customWidth="1" min="12" max="12"/>
-    <col width="9.6640625" bestFit="1" customWidth="1" min="13" max="13"/>
-    <col width="6.5" bestFit="1" customWidth="1" min="14" max="14"/>
-    <col width="10.1640625" bestFit="1" customWidth="1" min="15" max="15"/>
-    <col width="10.6640625" bestFit="1" customWidth="1" min="16" max="16"/>
+    <col width="12.5" bestFit="1" customWidth="1" min="10" max="10"/>
+    <col width="8.6640625" customWidth="1" min="11" max="11"/>
+    <col width="10.6640625" bestFit="1" customWidth="1" min="12" max="12"/>
+    <col width="11.33203125" bestFit="1" customWidth="1" min="13" max="13"/>
+    <col width="9.6640625" bestFit="1" customWidth="1" min="14" max="14"/>
+    <col width="6.5" bestFit="1" customWidth="1" min="15" max="15"/>
+    <col width="10.1640625" bestFit="1" customWidth="1" min="16" max="16"/>
+    <col width="12.5" customWidth="1" min="17" max="17"/>
+    <col width="10.6640625" customWidth="1" min="18" max="18"/>
+    <col width="12.5" customWidth="1" min="19" max="19"/>
+    <col width="12.5" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -626,21 +630,25 @@
       <c r="G1" s="17" t="n"/>
       <c r="H1" s="17" t="n"/>
       <c r="I1" s="17" t="n"/>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="17" t="n"/>
+      <c r="K1" s="11" t="inlineStr">
         <is>
           <t>Night (Net)</t>
         </is>
       </c>
-      <c r="K1" s="17" t="n"/>
       <c r="L1" s="17" t="n"/>
       <c r="M1" s="17" t="n"/>
       <c r="N1" s="17" t="n"/>
       <c r="O1" s="17" t="n"/>
-      <c r="P1" s="11" t="inlineStr">
+      <c r="P1" s="17" t="n"/>
+      <c r="Q1" s="17" t="n"/>
+      <c r="R1" s="11" t="inlineStr">
         <is>
           <t>Day-Averaged (Net)</t>
         </is>
       </c>
+      <c r="S1" s="17" t="n"/>
+      <c r="T1" s="17" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1" thickBot="1">
       <c r="A2" s="18" t="n"/>
@@ -676,39 +684,59 @@
           <t>Calcification (mg cm-2 hr-1)</t>
         </is>
       </c>
-      <c r="J2" s="14" t="inlineStr">
+      <c r="J2" s="15" t="inlineStr">
+        <is>
+          <t>Net Photosynthesis (µmol O2 cm-2 hr-1)</t>
+        </is>
+      </c>
+      <c r="K2" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">pHT </t>
         </is>
       </c>
-      <c r="K2" s="14" t="inlineStr">
+      <c r="L2" s="14" t="inlineStr">
         <is>
           <t>AT (µmol kg-1)</t>
         </is>
       </c>
-      <c r="L2" s="15" t="inlineStr">
+      <c r="M2" s="15" t="inlineStr">
         <is>
           <t>DIC (µmol kg-1)</t>
         </is>
       </c>
-      <c r="M2" s="15" t="inlineStr">
+      <c r="N2" s="15" t="inlineStr">
         <is>
           <t>pCO2 (µatm)</t>
         </is>
       </c>
-      <c r="N2" s="15" t="inlineStr">
+      <c r="O2" s="15" t="inlineStr">
         <is>
           <t>ΩArag</t>
         </is>
       </c>
-      <c r="O2" s="15" t="inlineStr">
+      <c r="P2" s="15" t="inlineStr">
         <is>
           <t>Calcification (mg cm-2 hr-1)</t>
         </is>
       </c>
-      <c r="P2" s="15" t="inlineStr">
+      <c r="Q2" s="15" t="inlineStr">
+        <is>
+          <t>Respiration (µmol O2 cm-2 hr-1)</t>
+        </is>
+      </c>
+      <c r="R2" s="15" t="inlineStr">
         <is>
           <t>Calcification (mg cm-2 hr-1)</t>
+        </is>
+      </c>
+      <c r="S2" s="15" t="inlineStr">
+        <is>
+          <t>Gross Photosynthesis (µmol O2 cm-2 hr-1)</t>
+        </is>
+      </c>
+      <c r="T2" s="15" t="inlineStr">
+        <is>
+          <t>Photosynthesis:Respiration</t>
         </is>
       </c>
     </row>
@@ -760,37 +788,57 @@
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
+          <t>0.58 (0.77)</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
           <t>-0.04 (–)</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>1.7 (–)</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>24.7 (–)</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>47.3 (–)</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>-0.2 (–)</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>0.0003 (–)</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr">
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>0.19 (0.00)</t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
         <is>
           <t>-0.0024 (–)</t>
+        </is>
+      </c>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>0.77 (0.77)</t>
+        </is>
+      </c>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
         </is>
       </c>
     </row>
@@ -842,37 +890,57 @@
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
+          <t>1.88 (0.60)</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
           <t>-0.01 (0.01)</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>1.5 (0.2)</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>6.8 (4.3)</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>31.1 (26.1)</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>0.0 (0.0)</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr">
+      <c r="P4" s="4" t="inlineStr">
         <is>
           <t>-0.0002 (0.0003)</t>
         </is>
       </c>
-      <c r="P4" s="4" t="inlineStr">
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>0.30 (0.08)</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
         <is>
           <t>0.0000 (0.0020)</t>
+        </is>
+      </c>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>2.18 (0.68)</t>
+        </is>
+      </c>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
         </is>
       </c>
     </row>
@@ -924,37 +992,57 @@
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
+          <t>1.91 (0.74)</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
           <t>-0.05 (0.01)</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
+      <c r="L5" s="4" t="inlineStr">
         <is>
           <t>-10.5 (3.9)</t>
         </is>
       </c>
-      <c r="L5" s="4" t="inlineStr">
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>19.7 (1.9)</t>
         </is>
       </c>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>58.6 (12.5)</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="O5" s="4" t="inlineStr">
         <is>
           <t>-0.3 (0.1)</t>
         </is>
       </c>
-      <c r="O5" s="4" t="inlineStr">
+      <c r="P5" s="4" t="inlineStr">
         <is>
           <t>0.0228 (0.0086)</t>
         </is>
       </c>
-      <c r="P5" s="4" t="inlineStr">
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>0.77 (0.27)</t>
+        </is>
+      </c>
+      <c r="R5" s="4" t="inlineStr">
         <is>
           <t>0.0250 (0.0109)</t>
+        </is>
+      </c>
+      <c r="S5" s="4" t="inlineStr">
+        <is>
+          <t>2.68 (0.86)</t>
+        </is>
+      </c>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>3.65 (1.38)</t>
         </is>
       </c>
     </row>
@@ -996,37 +1084,57 @@
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
+          <t>1.50 (0.81)</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
           <t>-0.05 (0.01)</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="L6" s="4" t="inlineStr">
         <is>
           <t>-13.1 (9.7)</t>
         </is>
       </c>
-      <c r="L6" s="4" t="inlineStr">
+      <c r="M6" s="4" t="inlineStr">
         <is>
           <t>15.8 (7.4)</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="N6" s="4" t="inlineStr">
         <is>
           <t>60.4 (7.7)</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>-0.3 (0.1)</t>
         </is>
       </c>
-      <c r="O6" s="4" t="inlineStr">
+      <c r="P6" s="4" t="inlineStr">
         <is>
           <t>0.0240 (0.0148)</t>
         </is>
       </c>
-      <c r="P6" s="4" t="inlineStr">
+      <c r="Q6" s="4" t="inlineStr">
+        <is>
+          <t>0.85 (0.24)</t>
+        </is>
+      </c>
+      <c r="R6" s="4" t="inlineStr">
         <is>
           <t>0.0229 (0.0181)</t>
+        </is>
+      </c>
+      <c r="S6" s="4" t="inlineStr">
+        <is>
+          <t>2.35 (0.76)</t>
+        </is>
+      </c>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>2.99 (1.58)</t>
         </is>
       </c>
     </row>
@@ -1068,37 +1176,57 @@
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
+          <t>2.04 (0.96)</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
           <t>-0.06 (0.01)</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="L7" s="4" t="inlineStr">
         <is>
           <t>-11.6 (8.0)</t>
         </is>
       </c>
-      <c r="L7" s="4" t="inlineStr">
+      <c r="M7" s="4" t="inlineStr">
         <is>
           <t>25.7 (8.5)</t>
         </is>
       </c>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="N7" s="4" t="inlineStr">
         <is>
           <t>74.1 (13.9)</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="O7" s="4" t="inlineStr">
         <is>
           <t>-0.4 (0.1)</t>
         </is>
       </c>
-      <c r="O7" s="4" t="inlineStr">
+      <c r="P7" s="4" t="inlineStr">
         <is>
           <t>0.0191 (0.0106)</t>
         </is>
       </c>
-      <c r="P7" s="4" t="inlineStr">
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t>0.77 (0.23)</t>
+        </is>
+      </c>
+      <c r="R7" s="4" t="inlineStr">
         <is>
           <t>0.0217 (0.0087)</t>
+        </is>
+      </c>
+      <c r="S7" s="4" t="inlineStr">
+        <is>
+          <t>2.82 (1.11)</t>
+        </is>
+      </c>
+      <c r="T7" s="4" t="inlineStr">
+        <is>
+          <t>3.68 (1.05)</t>
         </is>
       </c>
     </row>
@@ -1140,37 +1268,57 @@
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
+          <t>1.75 (0.93)</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
           <t>-0.05 (0.01)</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr">
+      <c r="L8" s="4" t="inlineStr">
         <is>
           <t>-10.1 (6.2)</t>
         </is>
       </c>
-      <c r="L8" s="4" t="inlineStr">
+      <c r="M8" s="4" t="inlineStr">
         <is>
           <t>16.4 (5.2)</t>
         </is>
       </c>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="N8" s="4" t="inlineStr">
         <is>
           <t>54.5 (10.7)</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="O8" s="4" t="inlineStr">
         <is>
           <t>-0.3 (0.1)</t>
         </is>
       </c>
-      <c r="O8" s="4" t="inlineStr">
+      <c r="P8" s="4" t="inlineStr">
         <is>
           <t>0.0220 (0.0105)</t>
         </is>
       </c>
-      <c r="P8" s="4" t="inlineStr">
+      <c r="Q8" s="4" t="inlineStr">
+        <is>
+          <t>0.76 (0.15)</t>
+        </is>
+      </c>
+      <c r="R8" s="4" t="inlineStr">
         <is>
           <t>0.0195 (0.0108)</t>
+        </is>
+      </c>
+      <c r="S8" s="4" t="inlineStr">
+        <is>
+          <t>2.51 (0.90)</t>
+        </is>
+      </c>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>3.41 (1.36)</t>
         </is>
       </c>
     </row>
@@ -1217,37 +1365,57 @@
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
+          <t>2.50 (0.02)</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
           <t>-0.07 (0.01)</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="L9" s="4" t="inlineStr">
         <is>
           <t>-15.4 (3.4)</t>
         </is>
       </c>
-      <c r="L9" s="4" t="inlineStr">
+      <c r="M9" s="4" t="inlineStr">
         <is>
           <t>14.9 (6.6)</t>
         </is>
       </c>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="N9" s="4" t="inlineStr">
         <is>
           <t>175.6 (22.5)</t>
         </is>
       </c>
-      <c r="N9" s="4" t="inlineStr">
+      <c r="O9" s="4" t="inlineStr">
         <is>
           <t>-0.3 (0.0)</t>
         </is>
       </c>
-      <c r="O9" s="4" t="inlineStr">
+      <c r="P9" s="4" t="inlineStr">
         <is>
           <t>0.0271 (0.0062)</t>
         </is>
       </c>
-      <c r="P9" s="4" t="inlineStr">
+      <c r="Q9" s="4" t="inlineStr">
+        <is>
+          <t>0.81 (0.17)</t>
+        </is>
+      </c>
+      <c r="R9" s="4" t="inlineStr">
         <is>
           <t>0.0384 (0.0108)</t>
+        </is>
+      </c>
+      <c r="S9" s="4" t="inlineStr">
+        <is>
+          <t>3.26 (0.23)</t>
+        </is>
+      </c>
+      <c r="T9" s="4" t="inlineStr">
+        <is>
+          <t>4.42 (0.92)</t>
         </is>
       </c>
     </row>
@@ -1289,37 +1457,57 @@
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
           <t>-0.09 (–)</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="L10" s="4" t="inlineStr">
         <is>
           <t>-16.8 (–)</t>
         </is>
       </c>
-      <c r="L10" s="4" t="inlineStr">
+      <c r="M10" s="4" t="inlineStr">
         <is>
           <t>21.2 (–)</t>
         </is>
       </c>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="N10" s="4" t="inlineStr">
         <is>
           <t>223.2 (–)</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="O10" s="4" t="inlineStr">
         <is>
           <t>-0.3 (–)</t>
         </is>
       </c>
-      <c r="O10" s="4" t="inlineStr">
+      <c r="P10" s="4" t="inlineStr">
         <is>
           <t>0.0340 (–)</t>
         </is>
       </c>
-      <c r="P10" s="4" t="inlineStr">
+      <c r="Q10" s="4" t="inlineStr">
+        <is>
+          <t>1.05 (–)</t>
+        </is>
+      </c>
+      <c r="R10" s="4" t="inlineStr">
         <is>
           <t>0.0555 (–)</t>
+        </is>
+      </c>
+      <c r="S10" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T10" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
         </is>
       </c>
     </row>
@@ -1361,37 +1549,57 @@
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
+          <t>2.75 (–)</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
           <t>-0.08 (–)</t>
         </is>
       </c>
-      <c r="K11" s="4" t="inlineStr">
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>-16.7 (–)</t>
         </is>
       </c>
-      <c r="L11" s="4" t="inlineStr">
+      <c r="M11" s="4" t="inlineStr">
         <is>
           <t>17.5 (–)</t>
         </is>
       </c>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="N11" s="4" t="inlineStr">
         <is>
           <t>206.1 (–)</t>
         </is>
       </c>
-      <c r="N11" s="4" t="inlineStr">
+      <c r="O11" s="4" t="inlineStr">
         <is>
           <t>-0.3 (–)</t>
         </is>
       </c>
-      <c r="O11" s="4" t="inlineStr">
+      <c r="P11" s="4" t="inlineStr">
         <is>
           <t>0.0219 (–)</t>
         </is>
       </c>
-      <c r="P11" s="4" t="inlineStr">
+      <c r="Q11" s="4" t="inlineStr">
+        <is>
+          <t>0.52 (–)</t>
+        </is>
+      </c>
+      <c r="R11" s="4" t="inlineStr">
         <is>
           <t>0.0385 (–)</t>
+        </is>
+      </c>
+      <c r="S11" s="4" t="inlineStr">
+        <is>
+          <t>3.27 (–)</t>
+        </is>
+      </c>
+      <c r="T11" s="4" t="inlineStr">
+        <is>
+          <t>6.25 (–)</t>
         </is>
       </c>
     </row>
@@ -1433,37 +1641,57 @@
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
+          <t>2.69 (1.69)</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
           <t>-0.06 (0.00)</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr">
+      <c r="L12" s="4" t="inlineStr">
         <is>
           <t>-9.5 (4.6)</t>
         </is>
       </c>
-      <c r="L12" s="4" t="inlineStr">
+      <c r="M12" s="4" t="inlineStr">
         <is>
           <t>17.3 (2.9)</t>
         </is>
       </c>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="N12" s="4" t="inlineStr">
         <is>
           <t>152.8 (8.8)</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="O12" s="4" t="inlineStr">
         <is>
           <t>-0.2 (0.0)</t>
         </is>
       </c>
-      <c r="O12" s="4" t="inlineStr">
+      <c r="P12" s="4" t="inlineStr">
         <is>
           <t>0.0172 (0.0071)</t>
         </is>
       </c>
-      <c r="P12" s="4" t="inlineStr">
+      <c r="Q12" s="4" t="inlineStr">
+        <is>
+          <t>0.81 (0.04)</t>
+        </is>
+      </c>
+      <c r="R12" s="4" t="inlineStr">
         <is>
           <t>0.0326 (0.0233)</t>
+        </is>
+      </c>
+      <c r="S12" s="4" t="inlineStr">
+        <is>
+          <t>2.60 (0.82)</t>
+        </is>
+      </c>
+      <c r="T12" s="4" t="inlineStr">
+        <is>
+          <t>4.38 (2.21)</t>
         </is>
       </c>
     </row>
@@ -1515,37 +1743,57 @@
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
+          <t>1.07 (0.38)</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
           <t>-0.06 (0.02)</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr">
+      <c r="L13" s="4" t="inlineStr">
         <is>
           <t>-10.6 (4.2)</t>
         </is>
       </c>
-      <c r="L13" s="4" t="inlineStr">
+      <c r="M13" s="4" t="inlineStr">
         <is>
           <t>21.3 (7.5)</t>
         </is>
       </c>
-      <c r="M13" s="4" t="inlineStr">
+      <c r="N13" s="4" t="inlineStr">
         <is>
           <t>74.7 (24.3)</t>
         </is>
       </c>
-      <c r="N13" s="4" t="inlineStr">
+      <c r="O13" s="4" t="inlineStr">
         <is>
           <t>-0.3 (0.1)</t>
         </is>
       </c>
-      <c r="O13" s="4" t="inlineStr">
+      <c r="P13" s="4" t="inlineStr">
         <is>
           <t>0.0161 (0.0039)</t>
         </is>
       </c>
-      <c r="P13" s="4" t="inlineStr">
+      <c r="Q13" s="4" t="inlineStr">
+        <is>
+          <t>0.55 (0.14)</t>
+        </is>
+      </c>
+      <c r="R13" s="4" t="inlineStr">
         <is>
           <t>0.0279 (0.0031)</t>
+        </is>
+      </c>
+      <c r="S13" s="4" t="inlineStr">
+        <is>
+          <t>1.62 (0.48)</t>
+        </is>
+      </c>
+      <c r="T13" s="4" t="inlineStr">
+        <is>
+          <t>2.94 (0.55)</t>
         </is>
       </c>
     </row>
@@ -1587,37 +1835,57 @@
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
+          <t>0.90 (0.24)</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
           <t>-0.05 (0.02)</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr">
+      <c r="L14" s="4" t="inlineStr">
         <is>
           <t>-15.9 (11.5)</t>
         </is>
       </c>
-      <c r="L14" s="4" t="inlineStr">
+      <c r="M14" s="4" t="inlineStr">
         <is>
           <t>12.3 (7.8)</t>
         </is>
       </c>
-      <c r="M14" s="4" t="inlineStr">
+      <c r="N14" s="4" t="inlineStr">
         <is>
           <t>63.1 (23.2)</t>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="O14" s="4" t="inlineStr">
         <is>
           <t>-0.3 (0.1)</t>
         </is>
       </c>
-      <c r="O14" s="4" t="inlineStr">
+      <c r="P14" s="4" t="inlineStr">
         <is>
           <t>0.0214 (0.0130)</t>
         </is>
       </c>
-      <c r="P14" s="4" t="inlineStr">
+      <c r="Q14" s="4" t="inlineStr">
+        <is>
+          <t>0.43 (0.05)</t>
+        </is>
+      </c>
+      <c r="R14" s="4" t="inlineStr">
         <is>
           <t>0.0285 (0.0141)</t>
+        </is>
+      </c>
+      <c r="S14" s="4" t="inlineStr">
+        <is>
+          <t>1.33 (0.24)</t>
+        </is>
+      </c>
+      <c r="T14" s="4" t="inlineStr">
+        <is>
+          <t>3.09 (0.59)</t>
         </is>
       </c>
     </row>
@@ -1659,37 +1927,57 @@
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
+          <t>1.64 (0.44)</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
           <t>-0.06 (0.01)</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr">
+      <c r="L15" s="4" t="inlineStr">
         <is>
           <t>-17.2 (7.8)</t>
         </is>
       </c>
-      <c r="L15" s="4" t="inlineStr">
+      <c r="M15" s="4" t="inlineStr">
         <is>
           <t>17.8 (6.5)</t>
         </is>
       </c>
-      <c r="M15" s="4" t="inlineStr">
+      <c r="N15" s="4" t="inlineStr">
         <is>
           <t>80.3 (12.7)</t>
         </is>
       </c>
-      <c r="N15" s="4" t="inlineStr">
+      <c r="O15" s="4" t="inlineStr">
         <is>
           <t>-0.4 (0.0)</t>
         </is>
       </c>
-      <c r="O15" s="4" t="inlineStr">
+      <c r="P15" s="4" t="inlineStr">
         <is>
           <t>0.0259 (0.0110)</t>
         </is>
       </c>
-      <c r="P15" s="4" t="inlineStr">
+      <c r="Q15" s="4" t="inlineStr">
+        <is>
+          <t>0.58 (0.21)</t>
+        </is>
+      </c>
+      <c r="R15" s="4" t="inlineStr">
         <is>
           <t>0.0422 (0.0111)</t>
+        </is>
+      </c>
+      <c r="S15" s="4" t="inlineStr">
+        <is>
+          <t>2.22 (0.52)</t>
+        </is>
+      </c>
+      <c r="T15" s="4" t="inlineStr">
+        <is>
+          <t>3.57 (0.78)</t>
         </is>
       </c>
     </row>
@@ -1731,37 +2019,57 @@
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
+          <t>0.70 (0.46)</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
           <t>-0.05 (0.01)</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr">
+      <c r="L16" s="4" t="inlineStr">
         <is>
           <t>-24.3 (7.8)</t>
         </is>
       </c>
-      <c r="L16" s="4" t="inlineStr">
+      <c r="M16" s="4" t="inlineStr">
         <is>
           <t>5.9 (6.2)</t>
         </is>
       </c>
-      <c r="M16" s="4" t="inlineStr">
+      <c r="N16" s="4" t="inlineStr">
         <is>
           <t>64.2 (15.2)</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="O16" s="4" t="inlineStr">
         <is>
           <t>-0.3 (0.1)</t>
         </is>
       </c>
-      <c r="O16" s="4" t="inlineStr">
+      <c r="P16" s="4" t="inlineStr">
         <is>
           <t>0.0378 (0.0128)</t>
         </is>
       </c>
-      <c r="P16" s="4" t="inlineStr">
+      <c r="Q16" s="4" t="inlineStr">
+        <is>
+          <t>0.61 (0.13)</t>
+        </is>
+      </c>
+      <c r="R16" s="4" t="inlineStr">
         <is>
           <t>0.0494 (0.0090)</t>
+        </is>
+      </c>
+      <c r="S16" s="4" t="inlineStr">
+        <is>
+          <t>1.31 (0.51)</t>
+        </is>
+      </c>
+      <c r="T16" s="4" t="inlineStr">
+        <is>
+          <t>2.15 (0.65)</t>
         </is>
       </c>
     </row>
@@ -1808,37 +2116,57 @@
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
+          <t>0.95 (0.78)</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
           <t>-0.06 (0.01)</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="L17" s="4" t="inlineStr">
         <is>
           <t>-14.4 (10.9)</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr">
+      <c r="M17" s="4" t="inlineStr">
         <is>
           <t>7.3 (7.3)</t>
         </is>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="N17" s="4" t="inlineStr">
         <is>
           <t>130.2 (32.8)</t>
         </is>
       </c>
-      <c r="N17" s="4" t="inlineStr">
+      <c r="O17" s="4" t="inlineStr">
         <is>
           <t>-0.2 (0.1)</t>
         </is>
       </c>
-      <c r="O17" s="4" t="inlineStr">
+      <c r="P17" s="4" t="inlineStr">
         <is>
           <t>0.0187 (0.0109)</t>
         </is>
       </c>
-      <c r="P17" s="4" t="inlineStr">
+      <c r="Q17" s="4" t="inlineStr">
+        <is>
+          <t>0.40 (0.12)</t>
+        </is>
+      </c>
+      <c r="R17" s="4" t="inlineStr">
         <is>
           <t>0.0259 (0.0148)</t>
+        </is>
+      </c>
+      <c r="S17" s="4" t="inlineStr">
+        <is>
+          <t>1.35 (0.84)</t>
+        </is>
+      </c>
+      <c r="T17" s="4" t="inlineStr">
+        <is>
+          <t>2.67 (0.60)</t>
         </is>
       </c>
     </row>
@@ -1880,37 +2208,57 @@
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
+          <t>0.71 (0.32)</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
           <t>-0.05 (0.01)</t>
         </is>
       </c>
-      <c r="K18" s="4" t="inlineStr">
+      <c r="L18" s="4" t="inlineStr">
         <is>
           <t>-7.1 (5.3)</t>
         </is>
       </c>
-      <c r="L18" s="4" t="inlineStr">
+      <c r="M18" s="4" t="inlineStr">
         <is>
           <t>13.3 (4.2)</t>
         </is>
       </c>
-      <c r="M18" s="4" t="inlineStr">
+      <c r="N18" s="4" t="inlineStr">
         <is>
           <t>119.7 (14.7)</t>
         </is>
       </c>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="O18" s="4" t="inlineStr">
         <is>
           <t>-0.2 (0.0)</t>
         </is>
       </c>
-      <c r="O18" s="4" t="inlineStr">
+      <c r="P18" s="4" t="inlineStr">
         <is>
           <t>0.0123 (0.0074)</t>
         </is>
       </c>
-      <c r="P18" s="4" t="inlineStr">
+      <c r="Q18" s="4" t="inlineStr">
+        <is>
+          <t>0.48 (0.05)</t>
+        </is>
+      </c>
+      <c r="R18" s="4" t="inlineStr">
         <is>
           <t>0.0221 (0.0120)</t>
+        </is>
+      </c>
+      <c r="S18" s="4" t="inlineStr">
+        <is>
+          <t>1.19 (0.35)</t>
+        </is>
+      </c>
+      <c r="T18" s="4" t="inlineStr">
+        <is>
+          <t>2.45 (0.66)</t>
         </is>
       </c>
     </row>
@@ -1952,37 +2300,57 @@
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
+          <t>0.75 (0.67)</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
           <t>-0.06 (0.01)</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>-12.3 (4.6)</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>13.0 (3.5)</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="N19" s="4" t="inlineStr">
         <is>
           <t>152.5 (24.3)</t>
         </is>
       </c>
-      <c r="N19" s="4" t="inlineStr">
+      <c r="O19" s="4" t="inlineStr">
         <is>
           <t>-0.2 (0.0)</t>
         </is>
       </c>
-      <c r="O19" s="4" t="inlineStr">
+      <c r="P19" s="4" t="inlineStr">
         <is>
           <t>0.0191 (0.0053)</t>
         </is>
       </c>
-      <c r="P19" s="4" t="inlineStr">
+      <c r="Q19" s="4" t="inlineStr">
+        <is>
+          <t>0.52 (0.23)</t>
+        </is>
+      </c>
+      <c r="R19" s="4" t="inlineStr">
         <is>
           <t>0.0282 (0.0112)</t>
+        </is>
+      </c>
+      <c r="S19" s="4" t="inlineStr">
+        <is>
+          <t>1.14 (0.93)</t>
+        </is>
+      </c>
+      <c r="T19" s="4" t="inlineStr">
+        <is>
+          <t>2.01 (0.79)</t>
         </is>
       </c>
     </row>
@@ -2026,53 +2394,74 @@
       </c>
       <c r="J20" s="8" t="inlineStr">
         <is>
+          <t>0.86 (0.51)</t>
+        </is>
+      </c>
+      <c r="K20" s="8" t="inlineStr">
+        <is>
           <t>-0.08 (0.01)</t>
         </is>
       </c>
-      <c r="K20" s="8" t="inlineStr">
+      <c r="L20" s="8" t="inlineStr">
         <is>
           <t>-17.7 (10.4)</t>
         </is>
       </c>
-      <c r="L20" s="8" t="inlineStr">
+      <c r="M20" s="8" t="inlineStr">
         <is>
           <t>13.2 (8.7)</t>
         </is>
       </c>
-      <c r="M20" s="8" t="inlineStr">
+      <c r="N20" s="8" t="inlineStr">
         <is>
           <t>202.9 (32.0)</t>
         </is>
       </c>
-      <c r="N20" s="8" t="inlineStr">
+      <c r="O20" s="8" t="inlineStr">
         <is>
           <t>-0.3 (0.0)</t>
         </is>
       </c>
-      <c r="O20" s="8" t="inlineStr">
+      <c r="P20" s="8" t="inlineStr">
         <is>
           <t>0.0253 (0.0123)</t>
         </is>
       </c>
-      <c r="P20" s="8" t="inlineStr">
+      <c r="Q20" s="8" t="inlineStr">
+        <is>
+          <t>0.58 (0.22)</t>
+        </is>
+      </c>
+      <c r="R20" s="8" t="inlineStr">
         <is>
           <t>0.0447 (0.0143)</t>
+        </is>
+      </c>
+      <c r="S20" s="8" t="inlineStr">
+        <is>
+          <t>1.34 (0.69)</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>2.21 (0.68)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="B13:B16"/>
     <mergeCell ref="B5:B8"/>
     <mergeCell ref="B17:B20"/>
-    <mergeCell ref="J1:O1"/>
     <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A5:A12"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="B1:B2"/>
-    <mergeCell ref="A5:A12"/>
+    <mergeCell ref="R1:T1"/>
+    <mergeCell ref="D1:J1"/>
     <mergeCell ref="A1:A2"/>
+    <mergeCell ref="K1:Q1"/>
     <mergeCell ref="A13:A20"/>
-    <mergeCell ref="D1:I1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
